--- a/Vplan_8bit_timer.xlsx
+++ b/Vplan_8bit_timer.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns7="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ns8="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" ns1:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quang Tran\Projects\project1\ICTC-APB-8bit-Timer-Verification\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F95CFC-5BCD-4484-B0CF-1ABF95835C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <ns1:AlternateContent>
+    <ns1:Choice Requires="x15">
+      <ns2:absPath url="C:\Users\Quang Tran\Projects\project1\ICTC-APB-8bit-Timer-Verification\"/>
+    </ns1:Choice>
+  </ns1:AlternateContent>
+  <ns3:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F95CFC-5BCD-4484-B0CF-1ABF95835C37}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" ns6:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Vplan" sheetId="1" r:id="rId1"/>
-    <sheet name="Coverage" sheetId="2" r:id="rId2"/>
+    <sheet name="Vplan" sheetId="1" ns7:id="rId1"/>
+    <sheet name="Coverage" sheetId="2" ns7:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <ns8:calcFeatures>
+        <ns8:feature name="microsoft.com:RD"/>
+        <ns8:feature name="microsoft.com:Single"/>
+        <ns8:feature name="microsoft.com:FV"/>
+        <ns8:feature name="microsoft.com:CNMTM"/>
+        <ns8:feature name="microsoft.com:LET_WF"/>
+        <ns8:feature name="microsoft.com:LAMBDA_WF"/>
+        <ns8:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </ns8:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1010,7 +1010,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1031,8 +1031,8 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <f>COUNTA($D$9:$D$42)</f>
-        <v>31</v>
+        <f>COUNTA($D$9:$D$68)</f>
+        <v>56</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -1043,7 +1043,8 @@
         <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>2</v>
+        <f>COUNTIF($H$9:$H$68,"Passed")</f>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -1054,6 +1055,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
+        <f>COUNTIF($H$9:$H$68,"Failed")</f>
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -1065,7 +1067,8 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>29</v>
+        <f>COUNTIF($H$9:$H$68,"Not Yet")</f>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
@@ -1106,11 +1109,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>1</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>18</v>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Register test</t>
+        </is>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
@@ -1122,687 +1125,1340 @@
       <c r="J8" s="6"/>
     </row>
     <row r="9" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="8"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Read default value</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>1. Wait for reset (presetn) release and clocks stable
+2. Read TCR(0x00), TSR(0x01), TDR(0x02), TIE(0x03) via APB
+Pass condition: TCR=8'h00, TSR=8'h00, TDR=8'h00, TIE=8'h00 (matching default value in RTL spec)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>default_value_register_test</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Seed=337600. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="8"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Read and Write value check</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>1. Write a walking-1/walking-0 and random pattern to every RW field:
+   TCR[4:3] clk_div, TCR[2] load, TCR[1] count_down, TCR[0] timer_en, TDR[7:0] data, TIE[1:0]
+2. Read back each register after each write
+Pass condition: Read data == written data on all RW bits; scoreboard matches reference model</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>rw_register_test</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Seed=922115. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>1.3</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>1.6</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>1.7</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>1.8</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>2</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>2.1</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I19" s="7"/>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I20" s="7"/>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>2.4</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I21" s="7"/>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I22" s="7"/>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
-        <v>3</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>3.1</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I24" s="7"/>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>3.2</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I25" s="7"/>
-      <c r="J25" s="8"/>
-    </row>
-    <row r="26" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>3.3</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I26" s="7"/>
-      <c r="J26" s="8"/>
-    </row>
-    <row r="27" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <v>3.4</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I27" s="7"/>
-      <c r="J27" s="8"/>
-    </row>
-    <row r="28" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I28" s="7"/>
-      <c r="J28" s="8"/>
-    </row>
-    <row r="29" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <v>3.6</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I29" s="7"/>
-      <c r="J29" s="8"/>
-    </row>
-    <row r="30" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <v>3.7</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I30" s="7"/>
-      <c r="J30" s="8"/>
-    </row>
-    <row r="31" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I31" s="7"/>
-      <c r="J31" s="8"/>
-    </row>
-    <row r="32" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I32" s="7"/>
-      <c r="J32" s="8"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Reserved bit / reserved region check</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>1. Write 8'hFF to reserved bits TCR[7:5], TSR[7:2], TIE[7:2]
+2. Write random data to reserved address region 0x04 -&gt; 0xFF, then read back
+Pass condition: Reserved bits and reserved region read as 0; write does not affect any other register</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>reserved_region_test</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Seed=520074. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>W1C attribute check (TSR)</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1. Trigger overflow/underflow so TSR[0]/TSR[1] are set by HW
+2. Write 1'b0 to the set bit -&gt; read back
+3. Write 1'b1 to the set bit -&gt; read back
+Pass condition: Write 0 does not clear (bit stays 1); write 1 clears the bit to 0; SW cannot set the bit by writing 1 when it is 0</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>w1c_register_test</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Seed=626325. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Reset on the fly check</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure all registers with non-default random values, start the timer
+2. Assert presetn asynchronously at a random time
+Pass condition: All registers return to default value; counter = 0; interrupt = 1'b0</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>reset_on_the_fly_test</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Seed=732647. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>APB access while counting (CDC)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>1. Issue random APB reads/writes (TCR, TSR, TDR, TIE) while the counter is running, at each clk_div
+2. Sweep the alignment between the APB access and the clk_in edge
+Pass condition: prdata is stable and correct (no metastability); counting is not disturbed by the access</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>cdc_access_while_counting_test</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Random</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Seed=179231. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Random register access / regression</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>1. Randomize paddr (0x00-&gt;0xFF), pwrite, pwdata over N transfers, run with N different seeds
+Pass condition: All read/write behaviour matches the reference model (incl. reserved and W1C rules); all seeds pass and the functional coverage goal in the Coverage sheet is reached</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>random_register_test</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Random</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Seed=637066. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Clock divisor test</t>
+        </is>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>No Divide: count up from 0</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b00 (no divide), write TDR=0, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count up; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and overflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_no_divide_up_from0_test</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Seed=135111. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>No Divide: count down from 255</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b00 (no divide), write TDR=255, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count down; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and underflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_no_divide_down_from255_test</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Seed=288325. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>No Divide: count up from random TDR</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b00 (no divide), write TDR=a randomized high TDR value, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count up; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and overflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_no_divide_up_random_load_test</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Constrained random</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Seed=223812. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>No Divide: count down from random TDR</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b00 (no divide), write TDR=a randomized low TDR value, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count down; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and underflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_no_divide_down_random_load_test</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Constrained random</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Seed=433169. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 2: count up from 0</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b01 (divide by 2), write TDR=0, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count up; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and overflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by2_up_from0_test</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Seed=903692. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 2: count down from 255</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b01 (divide by 2), write TDR=255, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count down; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and underflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by2_down_from255_test</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Seed=316732. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 2: count up from random TDR</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b01 (divide by 2), write TDR=a randomized high TDR value, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count up; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and overflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by2_up_random_load_test</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Constrained random</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Seed=981727. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 2: count down from random TDR</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b01 (divide by 2), write TDR=a randomized low TDR value, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count down; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and underflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by2_down_random_load_test</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Constrained random</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Seed=905587. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 4: count up from 0</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b10 (divide by 4), write TDR=0, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count up; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and overflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by4_up_from0_test</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Seed=218187. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 4: count down from 255</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b10 (divide by 4), write TDR=255, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count down; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and underflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by4_down_from255_test</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>Seed=500522. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 4: count up from random TDR</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b10 (divide by 4), write TDR=a randomized high TDR value, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count up; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and overflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by4_up_random_load_test</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Constrained random</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>Seed=531684. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 4: count down from random TDR</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b10 (divide by 4), write TDR=a randomized low TDR value, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count down; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and underflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by4_down_random_load_test</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Constrained random</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>Seed=768103. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 8: count up from 0</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b11 (divide by 8), write TDR=0, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count up; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and overflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by8_up_from0_test</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>Seed=437093. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 8: count down from 255</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b11 (divide by 8), write TDR=255, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count down; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and underflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by8_down_from255_test</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>Seed=541004. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 8: count up from random TDR</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b11 (divide by 8), write TDR=a randomized high TDR value, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count up; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and overflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by8_up_random_load_test</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Constrained random</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Seed=956136. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Divide By 8: count down from random TDR</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>1. Configure clk_div=2'b11 (divide by 8), write TDR=a randomized low TDR value, assert load, and verify counter load
+2. Measure clk_in period against ker_clk and verify the expected divisor
+3. Count down; compare every DUT counter step through rollover and read TSR
+Pass condition: Clock period, every counter value, and underflow status are correct.</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_by8_down_random_load_test</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Constrained random</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Seed=839112. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
     </row>
     <row r="33" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I33" s="7"/>
-      <c r="J33" s="8"/>
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Change clk_div between runs</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>1. Run with clk_div = A, stop the timer (timer_en = 0)
+2. Re-program clk_div = B (random A/B) and re-enable
+Pass condition: New divider takes effect on the next enable; no glitch on clk_in; counter keeps its previous value across the stop</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>clkdiv_reconfig_test</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Random</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Seed=749943. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
-        <v>4</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>98</v>
+      <c r="A34" s="5"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Counter test</t>
+        </is>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5"/>
@@ -1813,256 +2469,1750 @@
       <c r="I34" s="5"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I35" s="7"/>
-      <c r="J35" s="8"/>
-    </row>
-    <row r="36" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
-        <v>4.2</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I36" s="7"/>
-      <c r="J36" s="8"/>
-    </row>
-    <row r="37" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
-        <v>4.3</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I37" s="7"/>
-      <c r="J37" s="8"/>
-    </row>
-    <row r="38" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I38" s="7"/>
-      <c r="J38" s="8"/>
-    </row>
-    <row r="39" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I39" s="7"/>
-      <c r="J39" s="8"/>
-    </row>
-    <row r="40" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I40" s="7"/>
-      <c r="J40" s="8"/>
+    <row r="35" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Count up basic</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>1. Program clk_div, count_down = 0, timer_en = 1
+2. Observe the counter for M clk_in cycles
+Pass condition: Counter increments by 1 every clk_in rising edge and matches the reference model</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>count_up_test</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>Seed=536477. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Count down basic</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>1. Program count_down = 1, timer_en = 1
+Pass condition: Counter decrements by 1 every clk_in rising edge and matches the reference model</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>count_down_test</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>Seed=640894. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Load initial value from TDR</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>1. Write initial value to TDR (random 8-bit)
+2. Set TCR.load = 1 while timer_en = 0
+3. Clear load and set timer_en = 1
+Pass condition: Counter starts from the TDR value, not from 0</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>load_counter_test</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Seed=722895. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Load while counting</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>1. Start the timer, let it count to a random value
+2. Write TDR = random value, then set TCR.load = 1
+Pass condition: Counter stops counting on load and is overwritten with the TDR data; counting resumes after load = 0</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>load_on_the_fly_test</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Seed=978851. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Hold load while enabled</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>1. Write TDR near rollover and set TCR.load = 1 while timer_en = 1
+2. Keep load asserted for many clk_in cycles, then read TSR
+3. Clear load and allow counting to resume
+Pass condition: Counter remains at TDR and no rollover status is set while load is held; counting resumes after load clears</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>load_hold_test</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>Seed=210404. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Timer enable / disable</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>1. Enable the timer, count some cycles, then write timer_en = 0
+2. Wait, then re-enable
+Pass condition: Counter freezes and holds its value while timer_en = 0; resumes from the held value when re-enabled</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>timer_enable_disable_test</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Seed=904151. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
     </row>
     <row r="41" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
-        <v>4.7</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I41" s="7"/>
-      <c r="J41" s="8"/>
-    </row>
-    <row r="42" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
-        <v>4.8</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I42" s="7"/>
-      <c r="J42" s="8"/>
-    </row>
-    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Overflow rollover (255 -&gt; 0)</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>1. Load TDR = 8'hFD, count up until the counter passes 255
+Pass condition: Counter wraps 255 -&gt; 0 and continues counting; TSR.overflow is set on the transition</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>counter_overflow_test</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>Seed=665179. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Underflow rollover (0 -&gt; 255)</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>1. Load TDR = 8'h02, count down until the counter passes 0
+Pass condition: Counter wraps 0 -&gt; 255 and continues counting; TSR.underflow is set on the transition</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>counter_underflow_test</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>Seed=147739. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Change count direction</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>1. Count up to a random value, set timer_en = 0
+2. Set count_down = 1, re-enable the timer
+Pass condition: Counter continues from the held value in the new direction</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>count_direction_change_test</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>Seed=392916. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Continuous rollover</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>1. Run the timer for several full 0 -&gt; 255 -&gt; 0 cycles (both directions) without clearing TSR
+Pass condition: Counter keeps counting correctly across repeated rollovers; status bit stays 1; no counter corruption</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>continuous_rollover_test</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>Seed=504538. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Counter random / stress</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>1. Randomize clk_div, count_down, load, TDR and enable/disable timing over many iterations
+Pass condition: Counter value always matches the reference model; multiple overflow/underflow rollovers handled correctly</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>counter_random_test</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Random</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>Seed=641303. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Interrupt test</t>
+        </is>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="6"/>
+    </row>
+    <row r="47" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Overflow interrupt</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>1. Set TIE.overflow_en = 1, count up to overflow (255 -&gt; 0)
+Pass condition: TSR.overflow = 1 and interrupt output asserts and stays asserted until the status bit is cleared</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>overflow_interrupt_test</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>Seed=619232. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Underflow interrupt</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>1. Set TIE.underflow_en = 1, count down to underflow (0 -&gt; 255)
+Pass condition: TSR.underflow = 1 and interrupt asserts until the status bit is cleared</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>underflow_interrupt_test</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>Seed=687440. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Polling mode (interrupt disabled)</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>1. Keep TIE = 8'h00, generate overflow and underflow
+2. Poll TSR periodically
+Pass condition: TSR status bits still set by HW, but interrupt output stays 1'b0</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>polling_mode_test</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>Seed=889571. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Clear interrupt - No divide</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>1. Set clk_div=2'b00, enable overflow interrupt, generate overflow, then write TSR[0]=1
+2. Verify TSR.overflow=0 and interrupt=0
+3. Reset; enable underflow interrupt, generate underflow, then write TSR[1]=1
+4. Verify TSR.underflow=0 and interrupt=0
+Pass condition: W1C clears both status sources and de-asserts interrupt for no divide.</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>interrupt_clear_no_divide_test</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>Seed=205259. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Clear interrupt - Divide by 2</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>1. Set clk_div=2'b01, enable overflow interrupt, generate overflow, then write TSR[0]=1
+2. Verify TSR.overflow=0 and interrupt=0
+3. Reset; enable underflow interrupt, generate underflow, then write TSR[1]=1
+4. Verify TSR.underflow=0 and interrupt=0
+Pass condition: W1C clears both status sources and de-asserts interrupt for divide-by-2.</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>interrupt_clear_by2_test</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>Seed=283530. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Clear interrupt - Divide by 4</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>1. Set clk_div=2'b10, enable overflow interrupt, generate overflow, then write TSR[0]=1
+2. Verify TSR.overflow=0 and interrupt=0
+3. Reset; enable underflow interrupt, generate underflow, then write TSR[1]=1
+4. Verify TSR.underflow=0 and interrupt=0
+Pass condition: W1C clears both status sources and de-asserts interrupt for divide-by-4.</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>interrupt_clear_by4_test</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>Seed=643487. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Clear interrupt - Divide by 8</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>1. Set clk_div=2'b11, enable overflow interrupt, generate overflow, then write TSR[0]=1
+2. Verify TSR.overflow=0 and interrupt=0
+3. Reset; enable underflow interrupt, generate underflow, then write TSR[1]=1
+4. Verify TSR.underflow=0 and interrupt=0
+Pass condition: W1C clears both status sources and de-asserts interrupt for divide-by-8.</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>interrupt_clear_by8_test</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>Seed=237126. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Enable interrupt after status is set</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>1. Generate overflow/underflow with TIE = 0 (status set, no interrupt)
+2. Then write TIE.overflow_en / underflow_en = 1
+Pass condition: Interrupt asserts as soon as enable is set while the status bit is still 1 (level-based enable)</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>interrupt_late_enable_test</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>Seed=762725. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Both overflow and underflow enabled</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>1. Set TIE = 8'h03, generate an overflow then switch direction and generate an underflow
+2. Clear only one status bit at a time
+Pass condition: Interrupt stays asserted while any enabled status bit is set; de-asserts only when all enabled status bits are cleared</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>interrupt_both_source_test</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>Seed=595932. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>TIE mask x status source cross</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>1. Iterate TIE through 00, 01, 10 and 11
+2. For each mask, independently generate overflow and underflow
+3. Verify TSR, expected interrupt gating and W1C clear
+Pass condition: All 8 TIE-mask x status-source combinations behave correctly.</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>interrupt_mask_source_cross_test</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>Seed=970665. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Status HW set vs SW clear race</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>1. Align a write-1-to-clear on TSR with an HW overflow/underflow event, sweeping the alignment
+Pass condition: HW set has priority over the SW clear (no event is lost), per the reference model</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>status_set_clear_race_test</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Random</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>Seed=177888. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Interrupt with clock divisor</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>1. Repeat 4.1 / 4.2 with clk_div = 2'b01/2'b10/2'b11
+Pass condition: Interrupt timing follows clk_in; CDC from clk_in domain to pclk domain is correct (no missed or duplicated interrupt)</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>interrupt_clkdiv_test</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Random</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>Seed=816910. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>APB protocol test</t>
+        </is>
+      </c>
+      <c r="C59" s="6"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="6"/>
+    </row>
+    <row r="60" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>WRITE in IDLE without slave select</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Drive a WRITE while PSEL=0 and PENABLE=0, then read back the target register. Pass: no register update.</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>apb_write_idle_no_select_test</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>Seed=781795. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>WRITE with PENABLE but without PSEL</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Drive a WRITE with PENABLE=1 and PSEL=0, then read back the target register. Pass: no register update and PRDATA remains zero.</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>apb_write_penable_without_psel_test</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>Seed=996862. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>WRITE SETUP without ACCESS</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Drive selected WRITE SETUP but never assert PENABLE. Pass: no register update and PRDATA remains zero.</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>apb_write_setup_no_access_test</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>Seed=141686. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Valid WRITE ACCESS</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Perform a valid APB SETUP-to-ACCESS WRITE followed by readback. Pass: PREADY is high and data is stored.</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>apb_write_access_test</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>Seed=488277. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>READ in IDLE without slave select</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Drive a READ address while PSEL=0 and PENABLE=0. Pass: PRDATA remains zero.</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>apb_read_idle_no_select_test</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>Seed=658124. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>READ with PENABLE but without PSEL</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Drive PENABLE=1 with PSEL=0 during READ. Pass: PRDATA remains zero and no transfer is accepted.</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>apb_read_penable_without_psel_test</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>Seed=767144. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>PRDATA active before READ ACCESS</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Drive selected READ SETUP with PENABLE=0. Pass: PRDATA remains zero before ACCESS.</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>apb_read_setup_prdata_early_test</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>Seed=607430. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Valid READ ACCESS</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Write a known TDR value and perform a valid APB READ ACCESS. Pass: PREADY is high and PRDATA matches.</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>apb_read_access_test</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>Seed=240040. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>PRDATA during WRITE SETUP/ACCESS</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Perform a valid WRITE and sample PRDATA in both SETUP and ACCESS. Pass: PRDATA remains zero and write data is stored.</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>apb_write_access_prdata_active_test</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Directed</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Quang</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>ver 20260820</t>
+        </is>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>Seed=463279. Full regression with merged functional coverage: TEST PASSED.</t>
+        </is>
+      </c>
+    </row>
     <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3002,8 +5152,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3012,305 +5162,762 @@
     <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F2" s="10"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F16" s="10"/>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25" ht="30">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Covergroup</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Coverpoint / Cross</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Bins</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Sampling event</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Merged Result</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>cg_reg_access</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>cp_addr</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>TCR, TSR, TDR, TIE, reserved</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Valid APB ACCESS (PSEL &amp; PENABLE &amp; PREADY)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>5 address classes</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>cg_reg_access</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>cp_dir</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>read, write</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Valid APB ACCESS</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Direction of accepted transfer</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>cg_reg_access</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>cx_addr_dir</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>9 legal address x direction combinations</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Valid APB ACCESS</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Reserved WRITE is ignored; reserved READ remains required</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>100% (9/9)</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>cg_config</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>cp_clk_div</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>2'b00, 2'b01, 2'b10, 2'b11</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Accepted TCR WRITE</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>All supported divider modes</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>100% (4/4)</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>cg_config</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>cp_count_down</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>up, down</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Accepted TCR WRITE</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Both count directions</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>cg_config</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>cp_load</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>clear, set</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Accepted TCR WRITE</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Both load states</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>cg_config</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>cp_timer_en</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>0-&gt;1 start, 1-&gt;0 stop</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Accepted TCR WRITE</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Previous/current pair; reset jumps are not sampled as transitions</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>cg_config</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>cx_clkdiv_direction</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>4 dividers x 2 directions = 8 bins</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>TCR WRITE causing timer_en 0-&gt;1</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Key configuration cross</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>100% (8/8)</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>cg_counter</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>cp_cnt_value</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>0, 1, low[2:126], mid[127], high[128:254], 255</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Every DUT clk_in rising edge outside reset</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Samples actual internal DUT counter</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>100% (6/6)</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>cg_counter</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>cp_cnt_transition</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>255-&gt;0 overflow, 0-&gt;255 underflow</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>DUT clk_in while timer_en=1 and load=0</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Previous/current DUT counter pair excludes load/reset jumps</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>cg_counter</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>cp_tdr_load_value</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>0x00, 0xFF, other[0x01:0xFE]</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>DUT clk_in while load=1</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Covers boundary and normal load values</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>100% (3/3)</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>cg_interrupt</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>cp_tie</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>00, 01, 10, 11</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>TIE WRITE and HW status event</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Current mask is resampled at status event for the cross</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>100% (4/4)</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>cg_interrupt</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>cp_status_src</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>overflow, underflow</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Actual DUT counter rollover</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Derived from qualified DUT counter transition</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>cg_interrupt</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>cx_tie_status</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>4 TIE masks x 2 sources = 8 bins</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Actual DUT counter rollover</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Covers polling, masked, enabled and dual-source modes</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>100% (8/8)</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>cg_interrupt</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>cp_int_out</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>0-&gt;1 asserted, 1-&gt;0 cleared</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Every pclk outside reset</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Previous/current actual interrupt pair</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>tb/scoreboard.sv</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>sim/coverage.rpt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Vplan_8bit_timer.xlsx
+++ b/Vplan_8bit_timer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quang Tran\Projects\project1\ICTC-APB-8bit-Timer-Verification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4237ED97-C178-4DBC-89C2-8D7D60B56DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61C13DC-755E-448F-A7D8-3D0863FD45D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="176">
   <si>
     <t>Total Items</t>
   </si>
@@ -611,6 +611,9 @@
   </si>
   <si>
     <t>interrupt signal change</t>
+  </si>
+  <si>
+    <t>NY</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1200,7 @@
         <v>24</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="8"/>
@@ -1225,7 +1228,7 @@
         <v>24</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="8"/>
@@ -1253,7 +1256,7 @@
         <v>24</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="8"/>
@@ -1281,7 +1284,7 @@
         <v>24</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="8"/>
@@ -1309,7 +1312,7 @@
         <v>24</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="8"/>
@@ -1337,7 +1340,7 @@
         <v>24</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="8"/>
@@ -1381,7 +1384,7 @@
         <v>24</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="8"/>
@@ -1409,7 +1412,7 @@
         <v>24</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="8"/>
@@ -1437,7 +1440,7 @@
         <v>24</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="8"/>
@@ -1465,7 +1468,7 @@
         <v>24</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="8"/>
@@ -1493,7 +1496,7 @@
         <v>24</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="8"/>
@@ -1537,7 +1540,7 @@
         <v>24</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="8"/>
@@ -1565,7 +1568,7 @@
         <v>24</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I25" s="7"/>
       <c r="J25" s="8"/>
@@ -1593,7 +1596,7 @@
         <v>24</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I26" s="7"/>
       <c r="J26" s="8"/>
@@ -1621,7 +1624,7 @@
         <v>24</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="8"/>
@@ -1649,7 +1652,7 @@
         <v>24</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I28" s="7"/>
       <c r="J28" s="8"/>
@@ -1677,7 +1680,7 @@
         <v>24</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I29" s="7"/>
       <c r="J29" s="8"/>
@@ -1705,7 +1708,7 @@
         <v>24</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="8"/>
@@ -1733,7 +1736,7 @@
         <v>24</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I31" s="7"/>
       <c r="J31" s="8"/>
@@ -1761,7 +1764,7 @@
         <v>24</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I32" s="7"/>
       <c r="J32" s="8"/>
@@ -1789,7 +1792,7 @@
         <v>24</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I33" s="7"/>
       <c r="J33" s="8"/>
@@ -1833,7 +1836,7 @@
         <v>24</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I35" s="7"/>
       <c r="J35" s="8"/>
@@ -1861,7 +1864,7 @@
         <v>24</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I36" s="7"/>
       <c r="J36" s="8"/>
@@ -1889,7 +1892,7 @@
         <v>24</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="8"/>
@@ -1917,7 +1920,7 @@
         <v>24</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="8"/>
@@ -1945,7 +1948,7 @@
         <v>24</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I39" s="7"/>
       <c r="J39" s="8"/>
@@ -1973,7 +1976,7 @@
         <v>24</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="8"/>
@@ -2001,7 +2004,7 @@
         <v>24</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I41" s="7"/>
       <c r="J41" s="8"/>
@@ -2029,7 +2032,7 @@
         <v>24</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="8"/>

--- a/Vplan_8bit_timer.xlsx
+++ b/Vplan_8bit_timer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quang Tran\Projects\project1\ICTC-APB-8bit-Timer-Verification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61C13DC-755E-448F-A7D8-3D0863FD45D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AD48AE-D187-495C-B64C-0630E48C937E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1043,7 +1043,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -1065,7 +1065,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>

--- a/Vplan_8bit_timer.xlsx
+++ b/Vplan_8bit_timer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quang Tran\Projects\project1\ICTC-APB-8bit-Timer-Verification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AD48AE-D187-495C-B64C-0630E48C937E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE4E075-C44D-43B2-95EC-FBF223E27EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1200,7 +1200,7 @@
         <v>24</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="8"/>

--- a/Vplan_8bit_timer.xlsx
+++ b/Vplan_8bit_timer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quang Tran\Projects\project1\ICTC-APB-8bit-Timer-Verification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE4E075-C44D-43B2-95EC-FBF223E27EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F95CFC-5BCD-4484-B0CF-1ABF95835C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
